--- a/Data/National Accounts/PSA-10MFG_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-10MFG_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BA400A-E945-477F-99AD-E4B9B82152B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5951FB02-FCEF-403F-AD9C-02F48A85AEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MFG" sheetId="1" r:id="rId1"/>
@@ -670,9 +670,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -680,6 +677,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23652,7 +23652,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -23662,7 +23662,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -23864,10 +23864,10 @@
         <v>2103183.0411664778</v>
       </c>
       <c r="Z12" s="9">
-        <v>2228956.9688645643</v>
+        <v>2228410.5610952163</v>
       </c>
       <c r="AA12" s="9">
-        <v>2440450.5554043413</v>
+        <v>2438274.7746898946</v>
       </c>
       <c r="AB12" s="10"/>
       <c r="AC12" s="10"/>
@@ -24016,10 +24016,10 @@
         <v>186406.40244344261</v>
       </c>
       <c r="Z13" s="9">
-        <v>204657.1675677959</v>
+        <v>203612.67366957793</v>
       </c>
       <c r="AA13" s="9">
-        <v>195602.93927849986</v>
+        <v>194656.72153498017</v>
       </c>
       <c r="AB13" s="10"/>
       <c r="AC13" s="10"/>
@@ -24168,10 +24168,10 @@
         <v>13975.066396461005</v>
       </c>
       <c r="Z14" s="9">
-        <v>14382.075022825285</v>
+        <v>14412.775793798392</v>
       </c>
       <c r="AA14" s="9">
-        <v>16049.648563902429</v>
+        <v>16118.327918106334</v>
       </c>
       <c r="AB14" s="10"/>
       <c r="AC14" s="10"/>
@@ -24320,10 +24320,10 @@
         <v>39306.481017148224</v>
       </c>
       <c r="Z15" s="9">
-        <v>37663.830022278278</v>
+        <v>37599.822890694966</v>
       </c>
       <c r="AA15" s="9">
-        <v>40591.573619657822</v>
+        <v>40256.323683234194</v>
       </c>
       <c r="AB15" s="10"/>
       <c r="AC15" s="10"/>
@@ -24472,10 +24472,10 @@
         <v>41563.322010886535</v>
       </c>
       <c r="Z16" s="9">
-        <v>43888.293777481296</v>
+        <v>43905.554471534822</v>
       </c>
       <c r="AA16" s="9">
-        <v>41927.022433126622</v>
+        <v>42042.289314955546</v>
       </c>
       <c r="AB16" s="10"/>
       <c r="AC16" s="10"/>
@@ -24624,10 +24624,10 @@
         <v>10361.537886590389</v>
       </c>
       <c r="Z17" s="9">
-        <v>11936.204341495037</v>
+        <v>11968.759657188084</v>
       </c>
       <c r="AA17" s="9">
-        <v>14044.879582514939</v>
+        <v>14126.241827093309</v>
       </c>
       <c r="AB17" s="10"/>
       <c r="AC17" s="10"/>
@@ -24776,10 +24776,10 @@
         <v>30676.962781957674</v>
       </c>
       <c r="Z18" s="9">
-        <v>26389.78195729079</v>
+        <v>26500.686631871744</v>
       </c>
       <c r="AA18" s="9">
-        <v>29004.465847074978</v>
+        <v>29064.655395295038</v>
       </c>
       <c r="AB18" s="10"/>
       <c r="AC18" s="10"/>
@@ -24928,10 +24928,10 @@
         <v>26843.197711509099</v>
       </c>
       <c r="Z19" s="9">
-        <v>27945.32781718711</v>
+        <v>28117.15527210357</v>
       </c>
       <c r="AA19" s="9">
-        <v>29135.744227243282</v>
+        <v>28882.283260443372</v>
       </c>
       <c r="AB19" s="10"/>
       <c r="AC19" s="10"/>
@@ -25080,10 +25080,10 @@
         <v>32992.020349153376</v>
       </c>
       <c r="Z20" s="9">
-        <v>37018.400290474536</v>
+        <v>37005.883345981725</v>
       </c>
       <c r="AA20" s="9">
-        <v>38251.055303494184</v>
+        <v>37118.38091885412</v>
       </c>
       <c r="AB20" s="10"/>
       <c r="AC20" s="10"/>
@@ -25232,10 +25232,10 @@
         <v>136166.77930683346</v>
       </c>
       <c r="Z21" s="9">
-        <v>147969.40875276463</v>
+        <v>148849.16128813018</v>
       </c>
       <c r="AA21" s="9">
-        <v>139904.61138249311</v>
+        <v>141081.03113872101</v>
       </c>
       <c r="AB21" s="10"/>
       <c r="AC21" s="10"/>
@@ -25384,10 +25384,10 @@
         <v>442344.55499518447</v>
       </c>
       <c r="Z22" s="9">
-        <v>461073.28673980158</v>
+        <v>460850.54792891251</v>
       </c>
       <c r="AA22" s="9">
-        <v>415032.0219772936</v>
+        <v>416772.46127471083</v>
       </c>
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
@@ -25536,10 +25536,10 @@
         <v>40565.633189774177</v>
       </c>
       <c r="Z23" s="9">
-        <v>41790.543313932554</v>
+        <v>41867.951113141797</v>
       </c>
       <c r="AA23" s="9">
-        <v>41173.374906336961</v>
+        <v>41388.390493044033</v>
       </c>
       <c r="AB23" s="10"/>
       <c r="AC23" s="10"/>
@@ -25688,10 +25688,10 @@
         <v>39118.77624454991</v>
       </c>
       <c r="Z24" s="9">
-        <v>38611.144802957191</v>
+        <v>38521.417714848809</v>
       </c>
       <c r="AA24" s="9">
-        <v>38043.544114456839</v>
+        <v>38276.612721536832</v>
       </c>
       <c r="AB24" s="10"/>
       <c r="AC24" s="10"/>
@@ -25840,10 +25840,10 @@
         <v>92109.176159616851</v>
       </c>
       <c r="Z25" s="9">
-        <v>83314.93161544895</v>
+        <v>82802.136265415291</v>
       </c>
       <c r="AA25" s="9">
-        <v>86193.992445274853</v>
+        <v>85633.773513857479</v>
       </c>
       <c r="AB25" s="10"/>
       <c r="AC25" s="10"/>
@@ -25992,10 +25992,10 @@
         <v>73529.682559120585</v>
       </c>
       <c r="Z26" s="9">
-        <v>67190.191734506225</v>
+        <v>67414.717873836547</v>
       </c>
       <c r="AA26" s="9">
-        <v>44822.17407570385</v>
+        <v>45547.775845614655</v>
       </c>
       <c r="AB26" s="10"/>
       <c r="AC26" s="10"/>
@@ -26144,10 +26144,10 @@
         <v>29436.322817594271</v>
       </c>
       <c r="Z27" s="9">
-        <v>30448.722139393369</v>
+        <v>30396.756557712593</v>
       </c>
       <c r="AA27" s="9">
-        <v>31023.469301596284</v>
+        <v>31616.396547469492</v>
       </c>
       <c r="AB27" s="10"/>
       <c r="AC27" s="10"/>
@@ -26296,10 +26296,10 @@
         <v>360997.98265814112</v>
       </c>
       <c r="Z28" s="9">
-        <v>376901.60826731857</v>
+        <v>376743.97793430008</v>
       </c>
       <c r="AA28" s="9">
-        <v>382436.39356333594</v>
+        <v>383101.86626150995</v>
       </c>
       <c r="AB28" s="10"/>
       <c r="AC28" s="10"/>
@@ -26448,10 +26448,10 @@
         <v>54544.368293739113</v>
       </c>
       <c r="Z29" s="9">
-        <v>58978.810408547084</v>
+        <v>58670.967108550169</v>
       </c>
       <c r="AA29" s="9">
-        <v>58664.997565336773</v>
+        <v>58193.575349562925</v>
       </c>
       <c r="AB29" s="10"/>
       <c r="AC29" s="10"/>
@@ -26600,10 +26600,10 @@
         <v>42746.736867806205</v>
       </c>
       <c r="Z30" s="9">
-        <v>50603.911738026167</v>
+        <v>51077.381158689117</v>
       </c>
       <c r="AA30" s="9">
-        <v>45042.214834636077</v>
+        <v>44968.462866520116</v>
       </c>
       <c r="AB30" s="10"/>
       <c r="AC30" s="10"/>
@@ -26752,10 +26752,10 @@
         <v>57326.249298612885</v>
       </c>
       <c r="Z31" s="9">
-        <v>59967.948827625543</v>
+        <v>60060.018618122762</v>
       </c>
       <c r="AA31" s="9">
-        <v>63924.415043571105</v>
+        <v>64072.404823952478</v>
       </c>
       <c r="AB31" s="10"/>
       <c r="AC31" s="10"/>
@@ -26904,10 +26904,10 @@
         <v>19279.455413816831</v>
       </c>
       <c r="Z32" s="9">
-        <v>22523.341358021033</v>
+        <v>22602.130068323571</v>
       </c>
       <c r="AA32" s="9">
-        <v>22587.605754798038</v>
+        <v>22983.543472877733</v>
       </c>
       <c r="AB32" s="10"/>
       <c r="AC32" s="10"/>
@@ -27056,10 +27056,10 @@
         <v>72696.890875136858</v>
       </c>
       <c r="Z33" s="9">
-        <v>73825.935570902438</v>
+        <v>73827.376829736706</v>
       </c>
       <c r="AA33" s="9">
-        <v>79476.674135885813</v>
+        <v>79843.012168742716</v>
       </c>
       <c r="AB33" s="10"/>
       <c r="AC33" s="10"/>
@@ -27306,10 +27306,10 @@
         <v>3946170.6404435537</v>
       </c>
       <c r="Z35" s="12">
-        <v>4146037.8349306383</v>
+        <v>4145218.4132876866</v>
       </c>
       <c r="AA35" s="12">
-        <v>4293383.3733605752</v>
+        <v>4294019.3050209768</v>
       </c>
       <c r="AB35" s="10"/>
       <c r="AC35" s="10"/>
@@ -27623,7 +27623,7 @@
     </row>
     <row r="42" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:96" x14ac:dyDescent="0.2">
@@ -27633,7 +27633,7 @@
     </row>
     <row r="45" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
@@ -27835,10 +27835,10 @@
         <v>1822714.3832008329</v>
       </c>
       <c r="Z51" s="9">
-        <v>1903695.6854249169</v>
+        <v>1903344.0332499216</v>
       </c>
       <c r="AA51" s="9">
-        <v>2071985.4532681161</v>
+        <v>2069727.8668031634</v>
       </c>
       <c r="AB51" s="10"/>
       <c r="AC51" s="10"/>
@@ -27987,10 +27987,10 @@
         <v>153428.56843799033</v>
       </c>
       <c r="Z52" s="9">
-        <v>162440.29422283522</v>
+        <v>161763.91326739942</v>
       </c>
       <c r="AA52" s="9">
-        <v>157422.43470796605</v>
+        <v>156782.65439039134</v>
       </c>
       <c r="AB52" s="10"/>
       <c r="AC52" s="10"/>
@@ -28139,10 +28139,10 @@
         <v>13758.891675729754</v>
       </c>
       <c r="Z53" s="9">
-        <v>13547.020644440841</v>
+        <v>13572.727044078261</v>
       </c>
       <c r="AA53" s="9">
-        <v>14894.253940744251</v>
+        <v>14961.460843141491</v>
       </c>
       <c r="AB53" s="10"/>
       <c r="AC53" s="10"/>
@@ -28291,10 +28291,10 @@
         <v>39432.365458272005</v>
       </c>
       <c r="Z54" s="9">
-        <v>38015.986374732871</v>
+        <v>37933.284256921834</v>
       </c>
       <c r="AA54" s="9">
-        <v>41201.517081122031</v>
+        <v>40880.421989360388</v>
       </c>
       <c r="AB54" s="10"/>
       <c r="AC54" s="10"/>
@@ -28443,10 +28443,10 @@
         <v>49837.781941557216</v>
       </c>
       <c r="Z55" s="9">
-        <v>51450.747185487569</v>
+        <v>51477.662554418785</v>
       </c>
       <c r="AA55" s="9">
-        <v>48886.974127668916</v>
+        <v>49100.903241819593</v>
       </c>
       <c r="AB55" s="10"/>
       <c r="AC55" s="10"/>
@@ -28595,10 +28595,10 @@
         <v>10942.933395335838</v>
       </c>
       <c r="Z56" s="9">
-        <v>12077.90069676261</v>
+        <v>12111.347252627005</v>
       </c>
       <c r="AA56" s="9">
-        <v>14103.487683247331</v>
+        <v>14186.71314526487</v>
       </c>
       <c r="AB56" s="10"/>
       <c r="AC56" s="10"/>
@@ -28747,10 +28747,10 @@
         <v>44071.498240620276</v>
       </c>
       <c r="Z57" s="9">
-        <v>38819.205691276096</v>
+        <v>38976.318096482973</v>
       </c>
       <c r="AA57" s="9">
-        <v>42811.421190137007</v>
+        <v>42917.658755338547</v>
       </c>
       <c r="AB57" s="10"/>
       <c r="AC57" s="10"/>
@@ -28899,10 +28899,10 @@
         <v>29601.043987528217</v>
       </c>
       <c r="Z58" s="9">
-        <v>31228.914381692633</v>
+        <v>31393.309813341013</v>
       </c>
       <c r="AA58" s="9">
-        <v>33334.317021707</v>
+        <v>32958.171462151993</v>
       </c>
       <c r="AB58" s="10"/>
       <c r="AC58" s="10"/>
@@ -29051,10 +29051,10 @@
         <v>32092.694842262725</v>
       </c>
       <c r="Z59" s="9">
-        <v>34406.653362367782</v>
+        <v>34396.428003024892</v>
       </c>
       <c r="AA59" s="9">
-        <v>35653.618405319547</v>
+        <v>34602.078675090983</v>
       </c>
       <c r="AB59" s="10"/>
       <c r="AC59" s="10"/>
@@ -29203,10 +29203,10 @@
         <v>136484.12095471291</v>
       </c>
       <c r="Z60" s="9">
-        <v>147870.76637623337</v>
+        <v>148635.40197370166</v>
       </c>
       <c r="AA60" s="9">
-        <v>134998.8203093044</v>
+        <v>136069.49534889593</v>
       </c>
       <c r="AB60" s="10"/>
       <c r="AC60" s="10"/>
@@ -29355,10 +29355,10 @@
         <v>458858.48002449644</v>
       </c>
       <c r="Z61" s="9">
-        <v>483382.86271329771</v>
+        <v>483188.62401030317</v>
       </c>
       <c r="AA61" s="9">
-        <v>436612.4154241443</v>
+        <v>438730.60569139937</v>
       </c>
       <c r="AB61" s="10"/>
       <c r="AC61" s="10"/>
@@ -29507,10 +29507,10 @@
         <v>57811.389674434031</v>
       </c>
       <c r="Z62" s="9">
-        <v>58744.263242797118</v>
+        <v>58828.301303241446</v>
       </c>
       <c r="AA62" s="9">
-        <v>60708.162860234195</v>
+        <v>60984.482053549546</v>
       </c>
       <c r="AB62" s="10"/>
       <c r="AC62" s="10"/>
@@ -29659,10 +29659,10 @@
         <v>33927.105249363318</v>
       </c>
       <c r="Z63" s="9">
-        <v>34346.945270353288</v>
+        <v>34274.15626431501</v>
       </c>
       <c r="AA63" s="9">
-        <v>34012.198041211486</v>
+        <v>34206.174605590757</v>
       </c>
       <c r="AB63" s="10"/>
       <c r="AC63" s="10"/>
@@ -29811,10 +29811,10 @@
         <v>88412.858078606834</v>
       </c>
       <c r="Z64" s="9">
-        <v>81238.45679361542</v>
+        <v>80789.799175468026</v>
       </c>
       <c r="AA64" s="9">
-        <v>83603.594703259936</v>
+        <v>83097.949125604355</v>
       </c>
       <c r="AB64" s="10"/>
       <c r="AC64" s="10"/>
@@ -29963,10 +29963,10 @@
         <v>103074.69320655862</v>
       </c>
       <c r="Z65" s="9">
-        <v>94578.184797933427</v>
+        <v>94823.000971075788</v>
       </c>
       <c r="AA65" s="9">
-        <v>62358.306310679902</v>
+        <v>63405.6155359818</v>
       </c>
       <c r="AB65" s="10"/>
       <c r="AC65" s="10"/>
@@ -30115,10 +30115,10 @@
         <v>30012.335146910573</v>
       </c>
       <c r="Z66" s="9">
-        <v>31277.62116287048</v>
+        <v>31237.201459848664</v>
       </c>
       <c r="AA66" s="9">
-        <v>32060.389161837058</v>
+        <v>32652.122623456704</v>
       </c>
       <c r="AB66" s="10"/>
       <c r="AC66" s="10"/>
@@ -30267,10 +30267,10 @@
         <v>404335.56977385108</v>
       </c>
       <c r="Z67" s="9">
-        <v>412476.97679023747</v>
+        <v>412269.07484274439</v>
       </c>
       <c r="AA67" s="9">
-        <v>414843.24020558066</v>
+        <v>415596.421341623</v>
       </c>
       <c r="AB67" s="10"/>
       <c r="AC67" s="10"/>
@@ -30419,10 +30419,10 @@
         <v>56937.634002551116</v>
       </c>
       <c r="Z68" s="9">
-        <v>63478.67353463469</v>
+        <v>63178.45348882518</v>
       </c>
       <c r="AA68" s="9">
-        <v>62839.973792838879</v>
+        <v>62372.075423517679</v>
       </c>
       <c r="AB68" s="10"/>
       <c r="AC68" s="10"/>
@@ -30571,10 +30571,10 @@
         <v>47183.96854997646</v>
       </c>
       <c r="Z69" s="9">
-        <v>54635.055723868951</v>
+        <v>55125.620142894986</v>
       </c>
       <c r="AA69" s="9">
-        <v>50360.129556203319</v>
+        <v>50588.71339981936</v>
       </c>
       <c r="AB69" s="10"/>
       <c r="AC69" s="10"/>
@@ -30723,10 +30723,10 @@
         <v>69245.936918795778</v>
       </c>
       <c r="Z70" s="9">
-        <v>70149.350764100323</v>
+        <v>70259.608616646277</v>
       </c>
       <c r="AA70" s="9">
-        <v>75698.966058828519</v>
+        <v>75883.084695965532</v>
       </c>
       <c r="AB70" s="10"/>
       <c r="AC70" s="10"/>
@@ -30875,10 +30875,10 @@
         <v>19856.296953808549</v>
       </c>
       <c r="Z71" s="9">
-        <v>23032.611235429405</v>
+        <v>23101.745620786456</v>
       </c>
       <c r="AA71" s="9">
-        <v>22999.223944237092</v>
+        <v>23348.005574360017</v>
       </c>
       <c r="AB71" s="10"/>
       <c r="AC71" s="10"/>
@@ -31027,10 +31027,10 @@
         <v>78847.404405572233</v>
       </c>
       <c r="Z72" s="9">
-        <v>79853.635910963145</v>
+        <v>79854.989600900371</v>
       </c>
       <c r="AA72" s="9">
-        <v>86403.023759447591</v>
+        <v>86724.173032295934</v>
       </c>
       <c r="AB72" s="10"/>
       <c r="AC72" s="10"/>
@@ -31277,10 +31277,10 @@
         <v>3780867.9541197671</v>
       </c>
       <c r="Z74" s="12">
-        <v>3920747.8123008478</v>
+        <v>3920535.0010089669</v>
       </c>
       <c r="AA74" s="12">
-        <v>4017791.9215538353</v>
+        <v>4019776.8477577833</v>
       </c>
       <c r="AB74" s="10"/>
       <c r="AC74" s="10"/>
@@ -31594,7 +31594,7 @@
     </row>
     <row r="81" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="1:91" x14ac:dyDescent="0.2">
@@ -31604,7 +31604,7 @@
     </row>
     <row r="84" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:91" x14ac:dyDescent="0.2">
@@ -31720,7 +31720,7 @@
         <v>66</v>
       </c>
       <c r="Z88" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AA88" s="16"/>
     </row>
@@ -31801,10 +31801,10 @@
         <v>7.1107544711930899</v>
       </c>
       <c r="Y90" s="17">
-        <v>5.9801703054969977</v>
+        <v>5.9541902667341873</v>
       </c>
       <c r="Z90" s="17">
-        <v>9.4884553400558644</v>
+        <v>9.4176637491582653</v>
       </c>
       <c r="AA90" s="17"/>
       <c r="AB90" s="10"/>
@@ -31946,10 +31946,10 @@
         <v>11.270145580620181</v>
       </c>
       <c r="Y91" s="17">
-        <v>9.7908467118723195</v>
+        <v>9.2305151543042427</v>
       </c>
       <c r="Z91" s="17">
-        <v>-4.4240953771124083</v>
+        <v>-4.3985239097304287</v>
       </c>
       <c r="AA91" s="17"/>
       <c r="AB91" s="10"/>
@@ -32091,10 +32091,10 @@
         <v>-7.884562226241016</v>
       </c>
       <c r="Y92" s="17">
-        <v>2.9123913605687761</v>
+        <v>3.1320738300623105</v>
       </c>
       <c r="Z92" s="17">
-        <v>11.594804911186984</v>
+        <v>11.833613099301914</v>
       </c>
       <c r="AA92" s="17"/>
       <c r="AB92" s="10"/>
@@ -32236,10 +32236,10 @@
         <v>-10.477627716832259</v>
       </c>
       <c r="Y93" s="17">
-        <v>-4.1790843452847071</v>
+        <v>-4.3419255102197951</v>
       </c>
       <c r="Z93" s="17">
-        <v>7.7733560172923859</v>
+        <v>7.0651949618535212</v>
       </c>
       <c r="AA93" s="17"/>
       <c r="AB93" s="10"/>
@@ -32381,10 +32381,10 @@
         <v>-21.006767744392903</v>
       </c>
       <c r="Y94" s="17">
-        <v>5.5938063997526228</v>
+        <v>5.6353350678629397</v>
       </c>
       <c r="Z94" s="17">
-        <v>-4.468780113208652</v>
+        <v>-4.2438028149428817</v>
       </c>
       <c r="AA94" s="17"/>
       <c r="AB94" s="10"/>
@@ -32526,10 +32526,10 @@
         <v>-12.727554456316142</v>
       </c>
       <c r="Y95" s="17">
-        <v>15.197227208352302</v>
+        <v>15.511421066922068</v>
       </c>
       <c r="Z95" s="17">
-        <v>17.666212647594364</v>
+        <v>18.025946143964092</v>
       </c>
       <c r="AA95" s="17"/>
       <c r="AB95" s="10"/>
@@ -32671,10 +32671,10 @@
         <v>-5.1505507439836578</v>
       </c>
       <c r="Y96" s="17">
-        <v>-13.975245382467733</v>
+        <v>-13.613721083699204</v>
       </c>
       <c r="Z96" s="17">
-        <v>9.9079404824783808</v>
+        <v>9.6751031361567357</v>
       </c>
       <c r="AA96" s="17"/>
       <c r="AB96" s="10"/>
@@ -32816,10 +32816,10 @@
         <v>0.51863375941229606</v>
       </c>
       <c r="Y97" s="17">
-        <v>4.1058078010037775</v>
+        <v>4.7459232476176254</v>
       </c>
       <c r="Z97" s="17">
-        <v>4.259804779688551</v>
+        <v>2.7212140806396832</v>
       </c>
       <c r="AA97" s="17"/>
       <c r="AB97" s="10"/>
@@ -32961,10 +32961,10 @@
         <v>7.9084854090594376</v>
       </c>
       <c r="Y98" s="17">
-        <v>12.204102382061251</v>
+        <v>12.166163073221298</v>
       </c>
       <c r="Z98" s="17">
-        <v>3.3298440865820851</v>
+        <v>0.30399915554133372</v>
       </c>
       <c r="AA98" s="17"/>
       <c r="AB98" s="10"/>
@@ -33106,10 +33106,10 @@
         <v>27.46437361197178</v>
       </c>
       <c r="Y99" s="17">
-        <v>8.6677745526576189</v>
+        <v>9.3138591114934712</v>
       </c>
       <c r="Z99" s="17">
-        <v>-5.4503139792540765</v>
+        <v>-5.2187933624780527</v>
       </c>
       <c r="AA99" s="17"/>
       <c r="AB99" s="10"/>
@@ -33251,10 +33251,10 @@
         <v>-5.7362916835856907</v>
       </c>
       <c r="Y100" s="17">
-        <v>4.2339690933509928</v>
+        <v>4.1836149500991411</v>
       </c>
       <c r="Z100" s="17">
-        <v>-9.9856717113369768</v>
+        <v>-9.564507811109479</v>
       </c>
       <c r="AA100" s="17"/>
       <c r="AB100" s="10"/>
@@ -33396,10 +33396,10 @@
         <v>7.0216679725248525</v>
       </c>
       <c r="Y101" s="17">
-        <v>3.0195760002759187</v>
+        <v>3.2103971292032156</v>
       </c>
       <c r="Z101" s="17">
-        <v>-1.4768135531509898</v>
+        <v>-1.1454122003769101</v>
       </c>
       <c r="AA101" s="17"/>
       <c r="AB101" s="10"/>
@@ -33541,10 +33541,10 @@
         <v>-1.8810700937200835</v>
       </c>
       <c r="Y102" s="17">
-        <v>-1.2976669781776309</v>
+        <v>-1.5270378755376441</v>
       </c>
       <c r="Z102" s="17">
-        <v>-1.4700436658818887</v>
+        <v>-0.63550359211626528</v>
       </c>
       <c r="AA102" s="17"/>
       <c r="AB102" s="10"/>
@@ -33686,10 +33686,10 @@
         <v>-4.9150775612741882</v>
       </c>
       <c r="Y103" s="17">
-        <v>-9.5476313119208385</v>
+        <v>-10.104356897160059</v>
       </c>
       <c r="Z103" s="17">
-        <v>3.4556360714722558</v>
+        <v>3.4197635183778488</v>
       </c>
       <c r="AA103" s="17"/>
       <c r="AB103" s="10"/>
@@ -33831,10 +33831,10 @@
         <v>-2.5272805927765347</v>
       </c>
       <c r="Y104" s="17">
-        <v>-8.6216757695331836</v>
+        <v>-8.3163213446044466</v>
       </c>
       <c r="Z104" s="17">
-        <v>-33.29059953748434</v>
+        <v>-32.436451145794067</v>
       </c>
       <c r="AA104" s="17"/>
       <c r="AB104" s="10"/>
@@ -33976,10 +33976,10 @@
         <v>-3.4326055085965947</v>
       </c>
       <c r="Y105" s="17">
-        <v>3.4392859735658874</v>
+        <v>3.262750398783723</v>
       </c>
       <c r="Z105" s="17">
-        <v>1.8875904202867417</v>
+        <v>4.0124017424070928</v>
       </c>
       <c r="AA105" s="17"/>
       <c r="AB105" s="10"/>
@@ -34121,10 +34121,10 @@
         <v>0.68196056078339495</v>
       </c>
       <c r="Y106" s="17">
-        <v>4.4054610754536725</v>
+        <v>4.361795919250369</v>
       </c>
       <c r="Z106" s="17">
-        <v>1.4684960675709817</v>
+        <v>1.6875885746257637</v>
       </c>
       <c r="AA106" s="17"/>
       <c r="AB106" s="10"/>
@@ -34266,10 +34266,10 @@
         <v>2.1635070908337894</v>
       </c>
       <c r="Y107" s="17">
-        <v>8.1299724490841356</v>
+        <v>7.5655818261346042</v>
       </c>
       <c r="Z107" s="17">
-        <v>-0.53207726815193723</v>
+        <v>-0.81367630791562817</v>
       </c>
       <c r="AA107" s="17"/>
       <c r="AB107" s="10"/>
@@ -34411,10 +34411,10 @@
         <v>-5.5322706151082883</v>
       </c>
       <c r="Y108" s="17">
-        <v>18.380759435552193</v>
+        <v>19.488374789040236</v>
       </c>
       <c r="Z108" s="17">
-        <v>-10.990646201785154</v>
+        <v>-11.960124332117942</v>
       </c>
       <c r="AA108" s="17"/>
       <c r="AB108" s="10"/>
@@ -34556,10 +34556,10 @@
         <v>10.365008529437276</v>
       </c>
       <c r="Y109" s="17">
-        <v>4.6081848391162481</v>
+        <v>4.7687915273675969</v>
       </c>
       <c r="Z109" s="17">
-        <v>6.597634725373382</v>
+        <v>6.6806276423946969</v>
       </c>
       <c r="AA109" s="17"/>
       <c r="AB109" s="10"/>
@@ -34701,10 +34701,10 @@
         <v>-10.035541419646407</v>
       </c>
       <c r="Y110" s="17">
-        <v>16.825609824432263</v>
+        <v>17.234276504125262</v>
       </c>
       <c r="Z110" s="17">
-        <v>0.28532354838249319</v>
+        <v>1.687510882386718</v>
       </c>
       <c r="AA110" s="17"/>
       <c r="AB110" s="10"/>
@@ -34846,10 +34846,10 @@
         <v>13.865471046777088</v>
       </c>
       <c r="Y111" s="17">
-        <v>1.5530852587695989</v>
+        <v>1.555067817881735</v>
       </c>
       <c r="Z111" s="17">
-        <v>7.6541374264826061</v>
+        <v>8.1482447261799393</v>
       </c>
       <c r="AA111" s="17"/>
       <c r="AB111" s="10"/>
@@ -35084,10 +35084,10 @@
         <v>3.974229411211482</v>
       </c>
       <c r="Y113" s="17">
-        <v>5.0648391237490813</v>
+        <v>5.0440741412479611</v>
       </c>
       <c r="Z113" s="17">
-        <v>3.5538879358152826</v>
+        <v>3.5896996707411688</v>
       </c>
       <c r="AA113" s="17"/>
       <c r="AB113" s="10"/>
@@ -35388,7 +35388,7 @@
     </row>
     <row r="120" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:92" x14ac:dyDescent="0.2">
@@ -35398,7 +35398,7 @@
     </row>
     <row r="123" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="124" spans="1:92" x14ac:dyDescent="0.2">
@@ -35514,7 +35514,7 @@
         <v>66</v>
       </c>
       <c r="Z127" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AA127" s="7"/>
     </row>
@@ -35595,10 +35595,10 @@
         <v>2.6518925251581322</v>
       </c>
       <c r="Y129" s="17">
-        <v>4.4428958793793214</v>
+        <v>4.4236031049196214</v>
       </c>
       <c r="Z129" s="17">
-        <v>8.8401612259595908</v>
+        <v>8.7416583994615564</v>
       </c>
       <c r="AA129" s="17"/>
       <c r="AB129" s="10"/>
@@ -35740,10 +35740,10 @@
         <v>-5.9161485981448436E-2</v>
       </c>
       <c r="Y130" s="17">
-        <v>5.8735644062839896</v>
+        <v>5.4327201995486973</v>
       </c>
       <c r="Z130" s="17">
-        <v>-3.0890485263377343</v>
+        <v>-3.0793387575719322</v>
       </c>
       <c r="AA130" s="17"/>
       <c r="AB130" s="10"/>
@@ -35885,10 +35885,10 @@
         <v>-12.687428798945405</v>
       </c>
       <c r="Y131" s="17">
-        <v>-1.5398844346063498</v>
+        <v>-1.353049620849049</v>
       </c>
       <c r="Z131" s="17">
-        <v>9.9448678175319714</v>
+        <v>10.23179641462788</v>
       </c>
       <c r="AA131" s="17"/>
       <c r="AB131" s="10"/>
@@ -36030,10 +36030,10 @@
         <v>-11.765444586456525</v>
       </c>
       <c r="Y132" s="17">
-        <v>-3.59192015766331</v>
+        <v>-3.8016517242327836</v>
       </c>
       <c r="Z132" s="17">
-        <v>8.3794503580378148</v>
+        <v>7.769265936684036</v>
       </c>
       <c r="AA132" s="17"/>
       <c r="AB132" s="10"/>
@@ -36175,10 +36175,10 @@
         <v>-21.868062670775927</v>
       </c>
       <c r="Y133" s="17">
-        <v>3.2364306377475032</v>
+        <v>3.2904365904256991</v>
       </c>
       <c r="Z133" s="17">
-        <v>-4.9829656478571138</v>
+        <v>-4.6170692192689273</v>
       </c>
       <c r="AA133" s="17"/>
       <c r="AB133" s="10"/>
@@ -36320,10 +36320,10 @@
         <v>-16.335087534569809</v>
       </c>
       <c r="Y134" s="17">
-        <v>10.371691578699767</v>
+        <v>10.67733682624052</v>
       </c>
       <c r="Z134" s="17">
-        <v>16.771018717082711</v>
+        <v>17.135714543959651</v>
       </c>
       <c r="AA134" s="17"/>
       <c r="AB134" s="10"/>
@@ -36465,10 +36465,10 @@
         <v>-5.6259408382023537</v>
       </c>
       <c r="Y135" s="17">
-        <v>-11.917662795732213</v>
+        <v>-11.561168436613585</v>
       </c>
       <c r="Z135" s="17">
-        <v>10.284124643380039</v>
+        <v>10.112142068163237</v>
       </c>
       <c r="AA135" s="17"/>
       <c r="AB135" s="10"/>
@@ -36610,10 +36610,10 @@
         <v>-2.6694082898083025</v>
       </c>
       <c r="Y136" s="17">
-        <v>5.4993681805624277</v>
+        <v>6.0547385645179759</v>
       </c>
       <c r="Z136" s="17">
-        <v>6.7418374339923304</v>
+        <v>4.9846978802660971</v>
       </c>
       <c r="AA136" s="17"/>
       <c r="AB136" s="10"/>
@@ -36755,10 +36755,10 @@
         <v>4.4921761866153957</v>
       </c>
       <c r="Y137" s="17">
-        <v>7.2102343897210375</v>
+        <v>7.1783724367340653</v>
       </c>
       <c r="Z137" s="17">
-        <v>3.6241974185017085</v>
+        <v>0.59788380365543503</v>
       </c>
       <c r="AA137" s="17"/>
       <c r="AB137" s="10"/>
@@ -36900,10 +36900,10 @@
         <v>35.755841724593722</v>
       </c>
       <c r="Y138" s="17">
-        <v>8.3428352997186153</v>
+        <v>8.9030730710576194</v>
       </c>
       <c r="Z138" s="17">
-        <v>-8.7048619428794893</v>
+        <v>-8.4541814789380112</v>
       </c>
       <c r="AA138" s="17"/>
       <c r="AB138" s="10"/>
@@ -37045,10 +37045,10 @@
         <v>-1.1323148043847198</v>
       </c>
       <c r="Y139" s="17">
-        <v>5.3446506398861828</v>
+        <v>5.3023197881202577</v>
       </c>
       <c r="Z139" s="17">
-        <v>-9.6756527582761578</v>
+        <v>-9.2009654428362211</v>
       </c>
       <c r="AA139" s="17"/>
       <c r="AB139" s="10"/>
@@ -37190,10 +37190,10 @@
         <v>8.8169228488545173</v>
       </c>
       <c r="Y140" s="17">
-        <v>1.613650136446438</v>
+        <v>1.759016059870163</v>
       </c>
       <c r="Z140" s="17">
-        <v>3.3431343062726597</v>
+        <v>3.6652099457940466</v>
       </c>
       <c r="AA140" s="17"/>
       <c r="AB140" s="10"/>
@@ -37335,10 +37335,10 @@
         <v>-7.9860265228926295</v>
       </c>
       <c r="Y141" s="17">
-        <v>1.237476695710285</v>
+        <v>1.0229314066168484</v>
       </c>
       <c r="Z141" s="17">
-        <v>-0.97460553335069733</v>
+        <v>-0.19834670239579566</v>
       </c>
       <c r="AA141" s="17"/>
       <c r="AB141" s="10"/>
@@ -37480,10 +37480,10 @@
         <v>-4.5284305083183511</v>
       </c>
       <c r="Y142" s="17">
-        <v>-8.1146582532291092</v>
+        <v>-8.6221156840798301</v>
       </c>
       <c r="Z142" s="17">
-        <v>2.9113525822543664</v>
+        <v>2.8569819131784726</v>
       </c>
       <c r="AA142" s="17"/>
       <c r="AB142" s="10"/>
@@ -37625,10 +37625,10 @@
         <v>3.9695891901517371</v>
       </c>
       <c r="Y143" s="17">
-        <v>-8.2430596146412398</v>
+        <v>-8.0055462488223839</v>
       </c>
       <c r="Z143" s="17">
-        <v>-34.06692416025048</v>
+        <v>-33.132663081057046</v>
       </c>
       <c r="AA143" s="17"/>
       <c r="AB143" s="10"/>
@@ -37770,10 +37770,10 @@
         <v>-8.6003428792495669</v>
       </c>
       <c r="Y144" s="17">
-        <v>4.2158866005138407</v>
+        <v>4.0812096324473401</v>
       </c>
       <c r="Z144" s="17">
-        <v>2.5026455653085264</v>
+        <v>4.5296028372667507</v>
       </c>
       <c r="AA144" s="17"/>
       <c r="AB144" s="10"/>
@@ -37915,10 +37915,10 @@
         <v>-2.8439030200247402</v>
       </c>
       <c r="Y145" s="17">
-        <v>2.0135272840180676</v>
+        <v>1.9621091147955667</v>
       </c>
       <c r="Z145" s="17">
-        <v>0.57367163465866611</v>
+        <v>0.80708127335230984</v>
       </c>
       <c r="AA145" s="17"/>
       <c r="AB145" s="10"/>
@@ -38060,10 +38060,10 @@
         <v>3.1042962218206753</v>
       </c>
       <c r="Y146" s="17">
-        <v>11.48807751967793</v>
+        <v>10.96079876798963</v>
       </c>
       <c r="Z146" s="17">
-        <v>-1.0061642851552932</v>
+        <v>-1.2763498008860381</v>
       </c>
       <c r="AA146" s="17"/>
       <c r="AB146" s="10"/>
@@ -38205,10 +38205,10 @@
         <v>-5.5643118343057409</v>
       </c>
       <c r="Y147" s="17">
-        <v>15.791565234705573</v>
+        <v>16.831249759135588</v>
       </c>
       <c r="Z147" s="17">
-        <v>-7.8245114076052857</v>
+        <v>-8.2301237270713585</v>
       </c>
       <c r="AA147" s="17"/>
       <c r="AB147" s="10"/>
@@ -38350,10 +38350,10 @@
         <v>12.497039104786325</v>
       </c>
       <c r="Y148" s="17">
-        <v>1.3046452766809438</v>
+        <v>1.4638717345094534</v>
       </c>
       <c r="Z148" s="17">
-        <v>7.9111427750636665</v>
+        <v>8.003853408865865</v>
       </c>
       <c r="AA148" s="17"/>
       <c r="AB148" s="10"/>
@@ -38495,10 +38495,10 @@
         <v>-13.955896365845149</v>
       </c>
       <c r="Y149" s="17">
-        <v>15.996508759966048</v>
+        <v>16.344682367149076</v>
       </c>
       <c r="Z149" s="17">
-        <v>-0.14495660457706094</v>
+        <v>1.0659798511155856</v>
       </c>
       <c r="AA149" s="17"/>
       <c r="AB149" s="10"/>
@@ -38640,10 +38640,10 @@
         <v>13.203574252129258</v>
       </c>
       <c r="Y150" s="17">
-        <v>1.2761758145076101</v>
+        <v>1.2778926623194309</v>
       </c>
       <c r="Z150" s="17">
-        <v>8.2017403137247413</v>
+        <v>8.6020716623048941</v>
       </c>
       <c r="AA150" s="17"/>
       <c r="AB150" s="10"/>
@@ -38878,10 +38878,10 @@
         <v>1.3866760800078026</v>
       </c>
       <c r="Y152" s="17">
-        <v>3.6996758384185853</v>
+        <v>3.6940472024952271</v>
       </c>
       <c r="Z152" s="17">
-        <v>2.4751428528130219</v>
+        <v>2.5313342878784653</v>
       </c>
       <c r="AA152" s="17"/>
       <c r="AB152" s="10"/>
@@ -39177,7 +39177,7 @@
     </row>
     <row r="158" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:92" x14ac:dyDescent="0.2">
@@ -39187,7 +39187,7 @@
     </row>
     <row r="161" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="162" spans="1:96" x14ac:dyDescent="0.2">
@@ -39389,10 +39389,10 @@
         <v>115.38741673136519</v>
       </c>
       <c r="Z167" s="17">
-        <v>117.08578140560564</v>
+        <v>117.07870580234778</v>
       </c>
       <c r="AA167" s="17">
-        <v>117.78318962399325</v>
+        <v>117.8065393908996</v>
       </c>
       <c r="AB167" s="10"/>
       <c r="AC167" s="10"/>
@@ -39541,10 +39541,10 @@
         <v>121.4939331971807</v>
       </c>
       <c r="Z168" s="17">
-        <v>125.98916330885714</v>
+        <v>125.87026955326036</v>
       </c>
       <c r="AA168" s="17">
-        <v>124.2535345367783</v>
+        <v>124.15705187021632</v>
       </c>
       <c r="AB168" s="10"/>
       <c r="AC168" s="10"/>
@@ -39693,10 +39693,10 @@
         <v>101.57116376686486</v>
       </c>
       <c r="Z169" s="17">
-        <v>106.16411829804892</v>
+        <v>106.18924072511015</v>
       </c>
       <c r="AA169" s="17">
-        <v>107.75731787409315</v>
+        <v>107.73231362293853</v>
       </c>
       <c r="AB169" s="10"/>
       <c r="AC169" s="10"/>
@@ -39845,10 +39845,10 @@
         <v>99.680758585844927</v>
       </c>
       <c r="Z170" s="17">
-        <v>99.073662461409512</v>
+        <v>99.120926719742116</v>
       </c>
       <c r="AA170" s="17">
-        <v>98.519609216662374</v>
+        <v>98.473356497424064</v>
       </c>
       <c r="AB170" s="10"/>
       <c r="AC170" s="10"/>
@@ -39997,10 +39997,10 @@
         <v>83.39721470675839</v>
       </c>
       <c r="Z171" s="17">
-        <v>85.301567379104313</v>
+        <v>85.290497456291391</v>
       </c>
       <c r="AA171" s="17">
-        <v>85.763177576983395</v>
+        <v>85.624268677704947</v>
       </c>
       <c r="AB171" s="10"/>
       <c r="AC171" s="10"/>
@@ -40149,10 +40149,10 @@
         <v>94.68702323461774</v>
       </c>
       <c r="Z172" s="17">
-        <v>98.826813046198055</v>
+        <v>98.822694185339344</v>
       </c>
       <c r="AA172" s="17">
-        <v>99.584442500687203</v>
+        <v>99.573746804123232</v>
       </c>
       <c r="AB172" s="10"/>
       <c r="AC172" s="10"/>
@@ -40301,10 +40301,10 @@
         <v>69.607260943271072</v>
       </c>
       <c r="Z173" s="17">
-        <v>67.981251773066049</v>
+        <v>67.99176506685744</v>
       </c>
       <c r="AA173" s="17">
-        <v>67.749364633933467</v>
+        <v>67.721903380108486</v>
       </c>
       <c r="AB173" s="10"/>
       <c r="AC173" s="10"/>
@@ -40453,10 +40453,10 @@
         <v>90.683280369499542</v>
       </c>
       <c r="Z174" s="17">
-        <v>89.485428393788595</v>
+        <v>89.564163317863361</v>
       </c>
       <c r="AA174" s="17">
-        <v>87.404653313491778</v>
+        <v>87.633148257665852</v>
       </c>
       <c r="AB174" s="10"/>
       <c r="AC174" s="10"/>
@@ -40605,10 +40605,10 @@
         <v>102.80227482083035</v>
       </c>
       <c r="Z175" s="17">
-        <v>107.5908194284404</v>
+        <v>107.58641374833269</v>
       </c>
       <c r="AA175" s="17">
-        <v>107.2851985698795</v>
+        <v>107.27211294844707</v>
       </c>
       <c r="AB175" s="10"/>
       <c r="AC175" s="10"/>
@@ -40757,10 +40757,10 @@
         <v>99.767488228183893</v>
       </c>
       <c r="Z176" s="17">
-        <v>100.06670850428966</v>
+        <v>100.14381453650346</v>
       </c>
       <c r="AA176" s="17">
-        <v>103.63395106857136</v>
+        <v>103.68307075511302</v>
       </c>
       <c r="AB176" s="10"/>
       <c r="AC176" s="10"/>
@@ -40909,10 +40909,10 @@
         <v>96.401085356768306</v>
       </c>
       <c r="Z177" s="17">
-        <v>95.384698611723778</v>
+        <v>95.376944950402148</v>
       </c>
       <c r="AA177" s="17">
-        <v>95.057311087710005</v>
+        <v>94.995073484311746</v>
       </c>
       <c r="AB177" s="10"/>
       <c r="AC177" s="10"/>
@@ -41061,10 +41061,10 @@
         <v>70.168929372257494</v>
       </c>
       <c r="Z178" s="17">
-        <v>71.139786265098266</v>
+        <v>71.169743449374195</v>
       </c>
       <c r="AA178" s="17">
-        <v>67.821810060582237</v>
+        <v>67.867085362308259</v>
       </c>
       <c r="AB178" s="10"/>
       <c r="AC178" s="10"/>
@@ -41213,10 +41213,10 @@
         <v>115.30242841830433</v>
       </c>
       <c r="Z179" s="17">
-        <v>112.41507650546312</v>
+        <v>112.39202335946601</v>
       </c>
       <c r="AA179" s="17">
-        <v>111.85264788932695</v>
+        <v>111.89971741324385</v>
       </c>
       <c r="AB179" s="10"/>
       <c r="AC179" s="10"/>
@@ -41365,10 +41365,10 @@
         <v>104.18074719145905</v>
       </c>
       <c r="Z180" s="17">
-        <v>102.55602445416802</v>
+        <v>102.49083066239173</v>
       </c>
       <c r="AA180" s="17">
-        <v>103.09842866351524</v>
+        <v>103.05160887234433</v>
       </c>
       <c r="AB180" s="10"/>
       <c r="AC180" s="10"/>
@@ -41517,10 +41517,10 @@
         <v>71.336309885268633</v>
       </c>
       <c r="Z181" s="17">
-        <v>71.041955264904132</v>
+        <v>71.095322003572008</v>
       </c>
       <c r="AA181" s="17">
-        <v>71.878434049173819</v>
+        <v>71.835555038128959</v>
       </c>
       <c r="AB181" s="10"/>
       <c r="AC181" s="10"/>
@@ -41669,10 +41669,10 @@
         <v>98.080748044106798</v>
       </c>
       <c r="Z182" s="17">
-        <v>97.349865518349915</v>
+        <v>97.309474399566966</v>
       </c>
       <c r="AA182" s="17">
-        <v>96.765729027784019</v>
+        <v>96.827997714172596</v>
       </c>
       <c r="AB182" s="10"/>
       <c r="AC182" s="10"/>
@@ -41821,10 +41821,10 @@
         <v>89.281777227774171</v>
       </c>
       <c r="Z183" s="17">
-        <v>91.375186852911185</v>
+        <v>91.383031355918462</v>
       </c>
       <c r="AA183" s="17">
-        <v>92.188170493947268</v>
+        <v>92.181223559333219</v>
       </c>
       <c r="AB183" s="10"/>
       <c r="AC183" s="10"/>
@@ -41973,10 +41973,10 @@
         <v>95.796689218409085</v>
       </c>
       <c r="Z184" s="17">
-        <v>92.911220610757667</v>
+        <v>92.865468951258393</v>
       </c>
       <c r="AA184" s="17">
-        <v>93.35617764376299</v>
+        <v>93.300687774806306</v>
       </c>
       <c r="AB184" s="10"/>
       <c r="AC184" s="10"/>
@@ -42125,10 +42125,10 @@
         <v>90.59589131959001</v>
       </c>
       <c r="Z185" s="17">
-        <v>92.62168962320348</v>
+        <v>92.656338425377996</v>
       </c>
       <c r="AA185" s="17">
-        <v>89.440228274964426</v>
+        <v>88.890307431065622</v>
       </c>
       <c r="AB185" s="10"/>
       <c r="AC185" s="10"/>
@@ -42277,10 +42277,10 @@
         <v>82.786444735145935</v>
       </c>
       <c r="Z186" s="17">
-        <v>85.486106677290564</v>
+        <v>85.482996277171154</v>
       </c>
       <c r="AA186" s="17">
-        <v>84.445558997322408</v>
+        <v>84.435688244179943</v>
       </c>
       <c r="AB186" s="10"/>
       <c r="AC186" s="10"/>
@@ -42429,10 +42429,10 @@
         <v>97.094918849503429</v>
       </c>
       <c r="Z187" s="17">
-        <v>97.78891818994019</v>
+        <v>97.837325539532642</v>
       </c>
       <c r="AA187" s="17">
-        <v>98.210295310672024</v>
+        <v>98.439001137285473</v>
       </c>
       <c r="AB187" s="10"/>
       <c r="AC187" s="10"/>
@@ -42581,10 +42581,10 @@
         <v>92.199472415352318</v>
       </c>
       <c r="Z188" s="17">
-        <v>92.451564326035708</v>
+        <v>92.45180194589156</v>
       </c>
       <c r="AA188" s="17">
-        <v>91.983672188550656</v>
+        <v>92.06546384594445</v>
       </c>
       <c r="AB188" s="10"/>
       <c r="AC188" s="10"/>
@@ -42831,10 +42831,10 @@
         <v>104.37208303304185</v>
       </c>
       <c r="Z190" s="17">
-        <v>105.74609828061298</v>
+        <v>105.7309375434959</v>
       </c>
       <c r="AA190" s="17">
-        <v>106.85927636840282</v>
+        <v>106.82233038423925</v>
       </c>
       <c r="AB190" s="10"/>
       <c r="AC190" s="10"/>
@@ -42952,7 +42952,7 @@
     </row>
     <row r="197" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="199" spans="1:96" x14ac:dyDescent="0.2">
@@ -42962,7 +42962,7 @@
     </row>
     <row r="200" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="201" spans="1:96" x14ac:dyDescent="0.2">
@@ -43164,10 +43164,10 @@
         <v>53.296809307011564</v>
       </c>
       <c r="Z206" s="17">
-        <v>53.761134307204259</v>
+        <v>53.758580101640597</v>
       </c>
       <c r="AA206" s="17">
-        <v>56.842129928269571</v>
+        <v>56.783041749226214</v>
       </c>
       <c r="AB206" s="10"/>
       <c r="AC206" s="10"/>
@@ -43316,10 +43316,10 @@
         <v>4.7237288862523776</v>
       </c>
       <c r="Z207" s="17">
-        <v>4.936210804531159</v>
+        <v>4.9119890285367891</v>
       </c>
       <c r="AA207" s="17">
-        <v>4.5559159820706832</v>
+        <v>4.5332055519025953</v>
       </c>
       <c r="AB207" s="10"/>
       <c r="AC207" s="10"/>
@@ -43468,10 +43468,10 @@
         <v>0.35414247557450262</v>
       </c>
       <c r="Z208" s="17">
-        <v>0.34688721124673222</v>
+        <v>0.34769641444218191</v>
       </c>
       <c r="AA208" s="17">
-        <v>0.37382286109101481</v>
+        <v>0.3753669178724755</v>
       </c>
       <c r="AB208" s="10"/>
       <c r="AC208" s="10"/>
@@ -43620,10 +43620,10 @@
         <v>0.9960664299283859</v>
       </c>
       <c r="Z209" s="17">
-        <v>0.90842948187684291</v>
+        <v>0.90706493945329936</v>
       </c>
       <c r="AA209" s="17">
-        <v>0.9454448878597449</v>
+        <v>0.93749750114450259</v>
       </c>
       <c r="AB209" s="10"/>
       <c r="AC209" s="10"/>
@@ -43772,10 +43772,10 @@
         <v>1.0532570889082173</v>
       </c>
       <c r="Z210" s="17">
-        <v>1.0585598956121327</v>
+        <v>1.0591855505319954</v>
       </c>
       <c r="AA210" s="17">
-        <v>0.97654969955103121</v>
+        <v>0.97908943412983018</v>
       </c>
       <c r="AB210" s="10"/>
       <c r="AC210" s="10"/>
@@ -43924,10 +43924,10 @@
         <v>0.26257196737507887</v>
       </c>
       <c r="Z211" s="17">
-        <v>0.2878942454632647</v>
+        <v>0.28873652637510439</v>
       </c>
       <c r="AA211" s="17">
-        <v>0.32712847563672237</v>
+        <v>0.32897480946523833</v>
       </c>
       <c r="AB211" s="10"/>
       <c r="AC211" s="10"/>
@@ -44076,10 +44076,10 @@
         <v>0.77738561195391065</v>
       </c>
       <c r="Z212" s="17">
-        <v>0.63650605730018095</v>
+        <v>0.63930736549182998</v>
       </c>
       <c r="AA212" s="17">
-        <v>0.67556198281851099</v>
+        <v>0.6768636405828421</v>
       </c>
       <c r="AB212" s="10"/>
       <c r="AC212" s="10"/>
@@ -44228,10 +44228,10 @@
         <v>0.6802340840610962</v>
       </c>
       <c r="Z213" s="17">
-        <v>0.67402491076530724</v>
+        <v>0.67830334782777058</v>
       </c>
       <c r="AA213" s="17">
-        <v>0.67861967342640905</v>
+        <v>0.67261652099867031</v>
       </c>
       <c r="AB213" s="10"/>
       <c r="AC213" s="10"/>
@@ -44380,10 +44380,10 @@
         <v>0.83605153844652402</v>
       </c>
       <c r="Z214" s="17">
-        <v>0.89286209543463657</v>
+        <v>0.89273663427137351</v>
       </c>
       <c r="AA214" s="17">
-        <v>0.8909303450708107</v>
+        <v>0.86442044812075647</v>
       </c>
       <c r="AB214" s="10"/>
       <c r="AC214" s="10"/>
@@ -44532,10 +44532,10 @@
         <v>3.4506054530761032</v>
       </c>
       <c r="Z215" s="17">
-        <v>3.5689353219623987</v>
+        <v>3.5908641342272194</v>
       </c>
       <c r="AA215" s="17">
-        <v>3.2586098006194373</v>
+        <v>3.2855239140111832</v>
       </c>
       <c r="AB215" s="10"/>
       <c r="AC215" s="10"/>
@@ -44684,10 +44684,10 @@
         <v>11.209463434289413</v>
       </c>
       <c r="Z216" s="17">
-        <v>11.120817153553912</v>
+        <v>11.117642111490074</v>
       </c>
       <c r="AA216" s="17">
-        <v>9.666782252720985</v>
+        <v>9.7058823370305003</v>
       </c>
       <c r="AB216" s="10"/>
       <c r="AC216" s="10"/>
@@ -44836,10 +44836,10 @@
         <v>1.0279746337886331</v>
       </c>
       <c r="Z217" s="17">
-        <v>1.007963385231184</v>
+        <v>1.0100300379572804</v>
       </c>
       <c r="AA217" s="17">
-        <v>0.95899600212289404</v>
+        <v>0.96386130459750807</v>
       </c>
       <c r="AB217" s="10"/>
       <c r="AC217" s="10"/>
@@ -44988,10 +44988,10 @@
         <v>0.99130979901449268</v>
       </c>
       <c r="Z218" s="17">
-        <v>0.93127815857481544</v>
+        <v>0.92929765995843905</v>
       </c>
       <c r="AA218" s="17">
-        <v>0.88609706625567153</v>
+        <v>0.89139358728034057</v>
       </c>
       <c r="AB218" s="10"/>
       <c r="AC218" s="10"/>
@@ -45140,10 +45140,10 @@
         <v>2.3341407291313607</v>
       </c>
       <c r="Z219" s="17">
-        <v>2.0095072677223356</v>
+        <v>1.9975337367022512</v>
       </c>
       <c r="AA219" s="17">
-        <v>2.0076006484789621</v>
+        <v>1.9942568356347703</v>
       </c>
       <c r="AB219" s="10"/>
       <c r="AC219" s="10"/>
@@ -45292,10 +45292,10 @@
         <v>1.8633173589993506</v>
       </c>
       <c r="Z220" s="17">
-        <v>1.6205880025605288</v>
+        <v>1.6263248676531881</v>
       </c>
       <c r="AA220" s="17">
-        <v>1.0439825698728606</v>
+        <v>1.060725921570866</v>
       </c>
       <c r="AB220" s="10"/>
       <c r="AC220" s="10"/>
@@ -45444,10 +45444,10 @@
         <v>0.74594652638451531</v>
       </c>
       <c r="Z221" s="17">
-        <v>0.73440531301622258</v>
+        <v>0.73329686224191237</v>
       </c>
       <c r="AA221" s="17">
-        <v>0.72258791269583678</v>
+        <v>0.73628911054266999</v>
       </c>
       <c r="AB221" s="10"/>
       <c r="AC221" s="10"/>
@@ -45596,10 +45596,10 @@
         <v>9.1480580935436837</v>
       </c>
       <c r="Z222" s="17">
-        <v>9.0906456543135707</v>
+        <v>9.0886399791776977</v>
       </c>
       <c r="AA222" s="17">
-        <v>8.9075761539550129</v>
+        <v>8.9217546323918651</v>
       </c>
       <c r="AB222" s="10"/>
       <c r="AC222" s="10"/>
@@ -45748,10 +45748,10 @@
         <v>1.3822100781634792</v>
       </c>
       <c r="Z223" s="17">
-        <v>1.4225343027901669</v>
+        <v>1.4153890400678939</v>
       </c>
       <c r="AA223" s="17">
-        <v>1.366404824906603</v>
+        <v>1.3552238873616018</v>
       </c>
       <c r="AB223" s="10"/>
       <c r="AC223" s="10"/>
@@ -45900,10 +45900,10 @@
         <v>1.0832460317276453</v>
       </c>
       <c r="Z224" s="17">
-        <v>1.2205366606084711</v>
+        <v>1.232199996867674</v>
       </c>
       <c r="AA224" s="17">
-        <v>1.049107683094697</v>
+        <v>1.0472347624040419</v>
       </c>
       <c r="AB224" s="10"/>
       <c r="AC224" s="10"/>
@@ -46052,10 +46052,10 @@
         <v>1.4527057880134995</v>
       </c>
       <c r="Z225" s="17">
-        <v>1.4463917411074176</v>
+        <v>1.4488987703421763</v>
       </c>
       <c r="AA225" s="17">
-        <v>1.4889053570246471</v>
+        <v>1.492131270789419</v>
       </c>
       <c r="AB225" s="10"/>
       <c r="AC225" s="10"/>
@@ -46204,10 +46204,10 @@
         <v>0.4885611183719567</v>
       </c>
       <c r="Z226" s="17">
-        <v>0.54324977857800572</v>
+        <v>0.5452578806431867</v>
       </c>
       <c r="AA226" s="17">
-        <v>0.52610269781517227</v>
+        <v>0.53524546212456903</v>
       </c>
       <c r="AB226" s="10"/>
       <c r="AC226" s="10"/>
@@ -46356,10 +46356,10 @@
         <v>1.8422135659842032</v>
       </c>
       <c r="Z227" s="17">
-        <v>1.7806382505464406</v>
+        <v>1.7810250141000941</v>
       </c>
       <c r="AA227" s="17">
-        <v>1.8511431946427082</v>
+        <v>1.8594004008175431</v>
       </c>
       <c r="AB227" s="10"/>
       <c r="AC227" s="10"/>
@@ -46923,7 +46923,7 @@
     </row>
     <row r="236" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="238" spans="1:96" x14ac:dyDescent="0.2">
@@ -46933,7 +46933,7 @@
     </row>
     <row r="239" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="240" spans="1:96" x14ac:dyDescent="0.2">
@@ -47135,10 +47135,10 @@
         <v>48.208887623666911</v>
       </c>
       <c r="Z245" s="17">
-        <v>48.554402796637767</v>
+        <v>48.548068892640615</v>
       </c>
       <c r="AA245" s="17">
-        <v>51.570252858361052</v>
+        <v>51.488625990710155</v>
       </c>
       <c r="AB245" s="10"/>
       <c r="AC245" s="10"/>
@@ -47287,10 +47287,10 @@
         <v>4.0580250434509129</v>
       </c>
       <c r="Z246" s="17">
-        <v>4.1430946849781938</v>
+        <v>4.1260673154497729</v>
       </c>
       <c r="AA246" s="17">
-        <v>3.9181330885618566</v>
+        <v>3.9002825362767122</v>
       </c>
       <c r="AB246" s="10"/>
       <c r="AC246" s="10"/>
@@ -47439,10 +47439,10 @@
         <v>0.36390828356588284</v>
       </c>
       <c r="Z247" s="17">
-        <v>0.34552134676805241</v>
+        <v>0.34619578808976986</v>
       </c>
       <c r="AA247" s="17">
-        <v>0.37070744905535247</v>
+        <v>0.37219630367011391</v>
       </c>
       <c r="AB247" s="10"/>
       <c r="AC247" s="10"/>
@@ -47591,10 +47591,10 @@
         <v>1.0429447930151887</v>
       </c>
       <c r="Z248" s="17">
-        <v>0.96961059967852425</v>
+        <v>0.96755377128783537</v>
       </c>
       <c r="AA248" s="17">
-        <v>1.0254766271018787</v>
+        <v>1.0169823733415284</v>
       </c>
       <c r="AB248" s="10"/>
       <c r="AC248" s="10"/>
@@ -47743,10 +47743,10 @@
         <v>1.3181571677808057</v>
       </c>
       <c r="Z249" s="17">
-        <v>1.3122687213920619</v>
+        <v>1.3130264757532015</v>
       </c>
       <c r="AA249" s="17">
-        <v>1.2167622187055032</v>
+        <v>1.2214833086868464</v>
       </c>
       <c r="AB249" s="10"/>
       <c r="AC249" s="10"/>
@@ -47895,10 +47895,10 @@
         <v>0.28942913447723112</v>
       </c>
       <c r="Z250" s="17">
-        <v>0.30805094525257992</v>
+        <v>0.30892077865674195</v>
       </c>
       <c r="AA250" s="17">
-        <v>0.35102583604660559</v>
+        <v>0.35292290300090084</v>
       </c>
       <c r="AB250" s="10"/>
       <c r="AC250" s="10"/>
@@ -48047,10 +48047,10 @@
         <v>1.1656449993869376</v>
       </c>
       <c r="Z251" s="17">
-        <v>0.99009698021091208</v>
+        <v>0.99415814643797962</v>
       </c>
       <c r="AA251" s="17">
-        <v>1.06554600203338</v>
+        <v>1.0676627181252079</v>
       </c>
       <c r="AB251" s="10"/>
       <c r="AC251" s="10"/>
@@ -48199,10 +48199,10 @@
         <v>0.78291663043333415</v>
       </c>
       <c r="Z252" s="17">
-        <v>0.79650403129004843</v>
+        <v>0.80074045519965531</v>
       </c>
       <c r="AA252" s="17">
-        <v>0.82966758041604427</v>
+        <v>0.81990052459095941</v>
       </c>
       <c r="AB252" s="10"/>
       <c r="AC252" s="10"/>
@@ -48351,10 +48351,10 @@
         <v>0.84881818756175798</v>
       </c>
       <c r="Z253" s="17">
-        <v>0.8775533395547982</v>
+        <v>0.87734015878375826</v>
       </c>
       <c r="AA253" s="17">
-        <v>0.8873933519068582</v>
+        <v>0.86079600897228636</v>
       </c>
       <c r="AB253" s="10"/>
       <c r="AC253" s="10"/>
@@ -48503,10 +48503,10 @@
         <v>3.6098621430561995</v>
       </c>
       <c r="Z254" s="17">
-        <v>3.7714939459331616</v>
+        <v>3.7912020154251822</v>
       </c>
       <c r="AA254" s="17">
-        <v>3.3600251816200362</v>
+        <v>3.3850012202740802</v>
       </c>
       <c r="AB254" s="10"/>
       <c r="AC254" s="10"/>
@@ -48655,10 +48655,10 @@
         <v>12.136326515304722</v>
       </c>
       <c r="Z255" s="17">
-        <v>12.328843523083668</v>
+        <v>12.324558354560091</v>
       </c>
       <c r="AA255" s="17">
-        <v>10.866974297048451</v>
+        <v>10.914302517467398</v>
       </c>
       <c r="AB255" s="10"/>
       <c r="AC255" s="10"/>
@@ -48807,10 +48807,10 @@
         <v>1.529050746441454</v>
       </c>
       <c r="Z256" s="17">
-        <v>1.4982923170547839</v>
+        <v>1.5005171816627507</v>
       </c>
       <c r="AA256" s="17">
-        <v>1.5109832476530045</v>
+        <v>1.5171111323646351</v>
       </c>
       <c r="AB256" s="10"/>
       <c r="AC256" s="10"/>
@@ -48959,10 +48959,10 @@
         <v>0.89733642277549397</v>
       </c>
       <c r="Z257" s="17">
-        <v>0.87603046445869615</v>
+        <v>0.87422140742256882</v>
       </c>
       <c r="AA257" s="17">
-        <v>0.84653955967081673</v>
+        <v>0.85094710231665804</v>
       </c>
       <c r="AB257" s="10"/>
       <c r="AC257" s="10"/>
@@ -49111,10 +49111,10 @@
         <v>2.3384275555635066</v>
       </c>
       <c r="Z258" s="17">
-        <v>2.0720143371307915</v>
+        <v>2.0606830229720283</v>
       </c>
       <c r="AA258" s="17">
-        <v>2.0808343571691785</v>
+        <v>2.0672279152002204</v>
       </c>
       <c r="AB258" s="10"/>
       <c r="AC258" s="10"/>
@@ -49263,10 +49263,10 @@
         <v>2.7262177483412189</v>
       </c>
       <c r="Z259" s="17">
-        <v>2.4122486149506068</v>
+        <v>2.4186240129643704</v>
       </c>
       <c r="AA259" s="17">
-        <v>1.552054151340011</v>
+        <v>1.5773416768482862</v>
       </c>
       <c r="AB259" s="10"/>
       <c r="AC259" s="10"/>
@@ -49415,10 +49415,10 @@
         <v>0.79379485110576464</v>
       </c>
       <c r="Z260" s="17">
-        <v>0.79774631422967113</v>
+        <v>0.79675864268039021</v>
       </c>
       <c r="AA260" s="17">
-        <v>0.79796041676140528</v>
+        <v>0.81228694676596136</v>
       </c>
       <c r="AB260" s="10"/>
       <c r="AC260" s="10"/>
@@ -49567,10 +49567,10 @@
         <v>10.694252607612832</v>
       </c>
       <c r="Z261" s="17">
-        <v>10.52036490324992</v>
+        <v>10.515633063769233</v>
       </c>
       <c r="AA261" s="17">
-        <v>10.325154918553988</v>
+        <v>10.338793348029784</v>
       </c>
       <c r="AB261" s="10"/>
       <c r="AC261" s="10"/>
@@ -49719,10 +49719,10 @@
         <v>1.5059408234691154</v>
       </c>
       <c r="Z262" s="17">
-        <v>1.6190450539939962</v>
+        <v>1.6114753081547781</v>
       </c>
       <c r="AA262" s="17">
-        <v>1.5640425143902483</v>
+        <v>1.551630296550133</v>
       </c>
       <c r="AB262" s="10"/>
       <c r="AC262" s="10"/>
@@ -49871,10 +49871,10 @@
         <v>1.2479665812862664</v>
       </c>
       <c r="Z263" s="17">
-        <v>1.3934855884496933</v>
+        <v>1.4060739192153153</v>
       </c>
       <c r="AA263" s="17">
-        <v>1.2534280156730244</v>
+        <v>1.258495566191381</v>
       </c>
       <c r="AB263" s="10"/>
       <c r="AC263" s="10"/>
@@ -50023,10 +50023,10 @@
         <v>1.8314825526594487</v>
       </c>
       <c r="Z264" s="17">
-        <v>1.789182934541611</v>
+        <v>1.7920923700098241</v>
       </c>
       <c r="AA264" s="17">
-        <v>1.8840937394675432</v>
+        <v>1.8877437123976877</v>
       </c>
       <c r="AB264" s="10"/>
       <c r="AC264" s="10"/>
@@ -50175,10 +50175,10 @@
         <v>0.52517827109440385</v>
       </c>
       <c r="Z265" s="17">
-        <v>0.58745454535911534</v>
+        <v>0.58924982470099418</v>
       </c>
       <c r="AA265" s="17">
-        <v>0.57243442152530399</v>
+        <v>0.58082840064575847</v>
       </c>
       <c r="AB265" s="10"/>
       <c r="AC265" s="10"/>
@@ -50327,10 +50327,10 @@
         <v>2.0854313179506128</v>
       </c>
       <c r="Z266" s="17">
-        <v>2.036694011801333</v>
+        <v>2.0368390941631525</v>
       </c>
       <c r="AA266" s="17">
-        <v>2.1505101669384663</v>
+        <v>2.1574374975732882</v>
       </c>
       <c r="AB266" s="10"/>
       <c r="AC266" s="10"/>
